--- a/docs/care_procedure_template.xlsx
+++ b/docs/care_procedure_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinjeong/Desktop/WHS_After_Mate/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\MS_project\Backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E1E878-B253-3646-AF42-A2655634FC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD494BCF-EA38-4782-8E56-D0458801884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사업장" sheetId="2" r:id="rId1"/>
@@ -154,9 +154,6 @@
     <t>더나부스터</t>
   </si>
   <si>
-    <t>피부 재생 효과로 잘 알려진 리쥬란 힐러에, 즉각적인 수분감을 채우는 물광주사(HA)와 잔주름 및 모공을 개선하는 더모톡신의 핵심 성분을 더나만의 최적의 비율로 배합한 시그니처 스킨부스터예요.리쥬란의 강력한 재생 효과는 그대로 누리면서, 특유의 통증은 줄이고 즉각적인 물광 효과는 더한, 가장 진보된 형태의 올인원 피부 솔루션이에요.</t>
-  </si>
-  <si>
     <t>레이저 제모</t>
   </si>
   <si>
@@ -331,12 +328,16 @@
     <t>비고</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>피부 재생 효과로 잘 알려진 리쥬란 힐러에, 즉각적인 수분감을 채우는 물광주사(HA)와 잔주름 및 모공을 개선하는 더모톡신의 핵심 성분을 더나만의 최적의 비율로 배합한 시그니처 스킨부스터예요.리쥬란의 강력한 재생 효과는 그대로 누리면서, 특유의 통증은 줄이고 즉각적인 물광 효과는 더한, 가장 진보된 형태의 올인원 피부 솔루션이에요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -470,9 +471,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -781,35 +780,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
@@ -818,15 +817,15 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>38</v>
@@ -835,27 +834,27 @@
         <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +866,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -875,7 +874,7 @@
     <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="36" customHeight="1">
+    <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -912,1035 +911,1035 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-    </row>
-    <row r="8" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-    </row>
-    <row r="9" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-    </row>
-    <row r="10" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-    </row>
-    <row r="11" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-    </row>
-    <row r="12" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-    </row>
-    <row r="17" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-    </row>
-    <row r="18" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-    </row>
-    <row r="19" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-    </row>
-    <row r="20" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-    </row>
-    <row r="21" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A21" s="9" t="s">
+    <row r="25" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-    </row>
-    <row r="22" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A22" s="9" t="s">
+      <c r="B25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-    </row>
-    <row r="23" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A23" s="9" t="s">
+      <c r="B26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A24" s="9" t="s">
+      <c r="B27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="B28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-    </row>
-    <row r="26" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A26" s="9" t="s">
+      <c r="B29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-    </row>
-    <row r="27" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="B30" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A28" s="9" t="s">
+      <c r="B31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+    </row>
+    <row r="32" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-    </row>
-    <row r="29" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A29" s="9" t="s">
+      <c r="B32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A30" s="9" t="s">
+      <c r="B33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+    </row>
+    <row r="34" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M30" s="9"/>
-    </row>
-    <row r="31" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A31" s="9" t="s">
+      <c r="B34" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A32" s="9" t="s">
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+    </row>
+    <row r="36" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A33" s="9" t="s">
+      <c r="B36" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-    </row>
-    <row r="34" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A34" s="9" t="s">
+      <c r="B37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-    </row>
-    <row r="35" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A35" s="9" t="s">
+      <c r="B38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-    </row>
-    <row r="36" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A36" s="9" t="s">
+      <c r="B39" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-    </row>
-    <row r="37" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A37" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-    </row>
-    <row r="38" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A38" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-    </row>
-    <row r="39" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A39" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9" t="s">
+      <c r="B40" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A40" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="9" t="s">
+      <c r="C40" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9" t="s">
+    </row>
+    <row r="41" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9" t="s">
+    </row>
+    <row r="42" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A42" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="9" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9" t="s">
+    </row>
+    <row r="43" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A43" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9" t="s">
+    </row>
+    <row r="44" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A44" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="9" t="s">
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9" t="s">
+    </row>
+    <row r="45" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A45" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="9" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9" t="s">
+    </row>
+    <row r="46" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A46" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="9" t="s">
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9" t="s">
+    </row>
+    <row r="47" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1">
-      <c r="A47" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="9" t="s">
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="20" customHeight="1">
+    </row>
+    <row r="48" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1955,7 +1954,7 @@
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="1:13" ht="20" customHeight="1">
+    <row r="49" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -1970,7 +1969,7 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="1:13" ht="20" customHeight="1">
+    <row r="50" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1985,7 +1984,7 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="1:13" ht="20" customHeight="1">
+    <row r="51" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -2000,7 +1999,7 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="1:13" ht="20" customHeight="1">
+    <row r="52" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2015,7 +2014,7 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -2030,7 +2029,7 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -2045,7 +2044,7 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -2060,7 +2059,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -2075,7 +2074,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -2090,7 +2089,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -2105,7 +2104,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -2120,7 +2119,7 @@
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
